--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J715"/>
+  <dimension ref="A1:J716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31900,6 +31900,50 @@
       </c>
       <c r="J715" t="inlineStr"/>
     </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>715</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>18:36:29</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0561 cargada con 106 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>TPM-0561</t>
+        </is>
+      </c>
+      <c r="H716" t="n">
+        <v>106</v>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J716"/>
+  <dimension ref="A1:J717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31944,6 +31944,50 @@
       </c>
       <c r="J716" t="inlineStr"/>
     </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>716</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>18:36:31</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0562 cargada con 65 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>TPM-0562</t>
+        </is>
+      </c>
+      <c r="H717" t="n">
+        <v>65</v>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J717"/>
+  <dimension ref="A1:J718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31988,6 +31988,50 @@
       </c>
       <c r="J717" t="inlineStr"/>
     </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>717</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>18:36:33</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0563 cargada con 67 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>TPM-0563</t>
+        </is>
+      </c>
+      <c r="H718" t="n">
+        <v>67</v>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J718"/>
+  <dimension ref="A1:J719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32032,6 +32032,50 @@
       </c>
       <c r="J718" t="inlineStr"/>
     </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>22:11:09</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0564 cargada con 305 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="H719" t="n">
+        <v>305</v>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J719"/>
+  <dimension ref="A1:J720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32076,6 +32076,50 @@
       </c>
       <c r="J719" t="inlineStr"/>
     </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>22:11:12</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0565 cargada con 84 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>TPM-0565</t>
+        </is>
+      </c>
+      <c r="H720" t="n">
+        <v>84</v>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J720"/>
+  <dimension ref="A1:J721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32120,6 +32120,50 @@
       </c>
       <c r="J720" t="inlineStr"/>
     </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>720</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>23:04:00</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Remisión E0137 generada con 6 tarima(s) y 799 piezas hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>E0137</t>
+        </is>
+      </c>
+      <c r="H721" t="n">
+        <v>799</v>
+      </c>
+      <c r="I721" t="inlineStr"/>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J721"/>
+  <dimension ref="A1:J722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32164,6 +32164,50 @@
         </is>
       </c>
     </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>721</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>23:04:02</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0566 marcada como Remesada en E0137 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>TPM-0566</t>
+        </is>
+      </c>
+      <c r="H722" t="n">
+        <v>0</v>
+      </c>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J722"/>
+  <dimension ref="A1:J723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32208,6 +32208,50 @@
         </is>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>722</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>23:04:04</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0565 marcada como Remesada en E0137 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>TPM-0565</t>
+        </is>
+      </c>
+      <c r="H723" t="n">
+        <v>0</v>
+      </c>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J723"/>
+  <dimension ref="A1:J724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32252,6 +32252,50 @@
         </is>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>723</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>23:04:06</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0564 marcada como Remesada en E0137 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="H724" t="n">
+        <v>0</v>
+      </c>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J724"/>
+  <dimension ref="A1:J725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32296,6 +32296,50 @@
         </is>
       </c>
     </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>724</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>23:04:08</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0563 marcada como Remesada en E0137 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>TPM-0563</t>
+        </is>
+      </c>
+      <c r="H725" t="n">
+        <v>0</v>
+      </c>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J725"/>
+  <dimension ref="A1:J726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32340,6 +32340,50 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>725</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>23:04:10</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0562 marcada como Remesada en E0137 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>TPM-0562</t>
+        </is>
+      </c>
+      <c r="H726" t="n">
+        <v>0</v>
+      </c>
+      <c r="I726" t="inlineStr"/>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J726"/>
+  <dimension ref="A1:J727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32384,6 +32384,50 @@
         </is>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>726</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>23:04:12</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0561 marcada como Remesada en E0137 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>TPM-0561</t>
+        </is>
+      </c>
+      <c r="H727" t="n">
+        <v>0</v>
+      </c>
+      <c r="I727" t="inlineStr"/>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J727"/>
+  <dimension ref="A1:J728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32428,6 +32428,50 @@
         </is>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>727</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>14:50:22</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Remisión E0138 generada con 3 tarima(s) y 88 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>E0138</t>
+        </is>
+      </c>
+      <c r="H728" t="n">
+        <v>88</v>
+      </c>
+      <c r="I728" t="inlineStr"/>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J728"/>
+  <dimension ref="A1:J729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32472,6 +32472,50 @@
         </is>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>728</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>14:50:24</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0480 marcada como Remesada en E0138 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>TPM-0480</t>
+        </is>
+      </c>
+      <c r="H729" t="n">
+        <v>0</v>
+      </c>
+      <c r="I729" t="inlineStr"/>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J729"/>
+  <dimension ref="A1:J730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32516,6 +32516,50 @@
         </is>
       </c>
     </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>729</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>15:00:18</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Remisión E0139 generada con 6 tarima(s) y 172 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>E0139</t>
+        </is>
+      </c>
+      <c r="H730" t="n">
+        <v>172</v>
+      </c>
+      <c r="I730" t="inlineStr"/>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J730"/>
+  <dimension ref="A1:J731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32560,6 +32560,50 @@
         </is>
       </c>
     </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>730</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>15:00:20</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0476 marcada como Remesada en E0139 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>TPM-0476</t>
+        </is>
+      </c>
+      <c r="H731" t="n">
+        <v>0</v>
+      </c>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J731"/>
+  <dimension ref="A1:J732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32604,6 +32604,50 @@
         </is>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>731</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>15:00:23</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0474 marcada como Remesada en E0139 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>TPM-0474</t>
+        </is>
+      </c>
+      <c r="H732" t="n">
+        <v>0</v>
+      </c>
+      <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J732"/>
+  <dimension ref="A1:J733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32648,6 +32648,50 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>732</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>16:55:55</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Remisión E0140 generada con 19 tarima(s) y 498 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>E0140</t>
+        </is>
+      </c>
+      <c r="H733" t="n">
+        <v>498</v>
+      </c>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J733"/>
+  <dimension ref="A1:J734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32692,6 +32692,50 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>733</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>16:55:57</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0533 marcada como Remesada en E0140 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>TPM-0533</t>
+        </is>
+      </c>
+      <c r="H734" t="n">
+        <v>0</v>
+      </c>
+      <c r="I734" t="inlineStr"/>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J734"/>
+  <dimension ref="A1:J735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32736,6 +32736,50 @@
         </is>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>734</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>16:55:59</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0538 marcada como Remesada en E0140 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>TPM-0538</t>
+        </is>
+      </c>
+      <c r="H735" t="n">
+        <v>0</v>
+      </c>
+      <c r="I735" t="inlineStr"/>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J735"/>
+  <dimension ref="A1:J736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32780,6 +32780,50 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>735</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>16:56:02</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0536 marcada como Remesada en E0140 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>TPM-0536</t>
+        </is>
+      </c>
+      <c r="H736" t="n">
+        <v>0</v>
+      </c>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J736"/>
+  <dimension ref="A1:J737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32824,6 +32824,50 @@
         </is>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>736</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>16:56:04</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0537 marcada como Remesada en E0140 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>TPM-0537</t>
+        </is>
+      </c>
+      <c r="H737" t="n">
+        <v>0</v>
+      </c>
+      <c r="I737" t="inlineStr"/>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J737"/>
+  <dimension ref="A1:J738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32868,6 +32868,50 @@
         </is>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>737</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>16:56:05</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0532 marcada como Remesada en E0140 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>TPM-0532</t>
+        </is>
+      </c>
+      <c r="H738" t="n">
+        <v>0</v>
+      </c>
+      <c r="I738" t="inlineStr"/>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J738"/>
+  <dimension ref="A1:J739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32912,6 +32912,50 @@
         </is>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>738</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>16:56:07</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0535 marcada como Remesada en E0140 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>TPM-0535</t>
+        </is>
+      </c>
+      <c r="H739" t="n">
+        <v>0</v>
+      </c>
+      <c r="I739" t="inlineStr"/>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J739"/>
+  <dimension ref="A1:J740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32956,6 +32956,50 @@
         </is>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>16:56:10</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0528 marcada como Remesada en E0140 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>TPM-0528</t>
+        </is>
+      </c>
+      <c r="H740" t="n">
+        <v>0</v>
+      </c>
+      <c r="I740" t="inlineStr"/>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J740"/>
+  <dimension ref="A1:J741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33000,6 +33000,50 @@
         </is>
       </c>
     </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>17:43:39</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Remisión E0141 generada con 3 tarima(s) y 74 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>E0141</t>
+        </is>
+      </c>
+      <c r="H741" t="n">
+        <v>74</v>
+      </c>
+      <c r="I741" t="inlineStr"/>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J741"/>
+  <dimension ref="A1:J742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33044,6 +33044,50 @@
         </is>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>17:43:42</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0306 marcada como Remesada en E0141 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>TPM-0306</t>
+        </is>
+      </c>
+      <c r="H742" t="n">
+        <v>0</v>
+      </c>
+      <c r="I742" t="inlineStr"/>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J742"/>
+  <dimension ref="A1:J743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33088,6 +33088,50 @@
         </is>
       </c>
     </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>18:36:24</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Remisión E0142 generada con 6 tarima(s) y 148 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>E0142</t>
+        </is>
+      </c>
+      <c r="H743" t="n">
+        <v>148</v>
+      </c>
+      <c r="I743" t="inlineStr"/>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J743"/>
+  <dimension ref="A1:J744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33132,6 +33132,50 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>18:36:26</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0548 marcada como Remesada en E0142 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>TPM-0548</t>
+        </is>
+      </c>
+      <c r="H744" t="n">
+        <v>0</v>
+      </c>
+      <c r="I744" t="inlineStr"/>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J744"/>
+  <dimension ref="A1:J745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33176,6 +33176,50 @@
         </is>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>15:43:37</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Remisión E0144 generada con 3 tarima(s) y 73 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>E0144</t>
+        </is>
+      </c>
+      <c r="H745" t="n">
+        <v>73</v>
+      </c>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J745"/>
+  <dimension ref="A1:J746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33220,6 +33220,50 @@
         </is>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>19:08:00</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Remisión E0145 generada con 3 tarima(s) y 88 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>E0145</t>
+        </is>
+      </c>
+      <c r="H746" t="n">
+        <v>88</v>
+      </c>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J746"/>
+  <dimension ref="A1:J747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33264,6 +33264,50 @@
         </is>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>21:11:49</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0567 cargada con 118 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="H747" t="n">
+        <v>118</v>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J747"/>
+  <dimension ref="A1:J748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33308,6 +33308,50 @@
       </c>
       <c r="J747" t="inlineStr"/>
     </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>21:11:52</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0568 cargada con 83 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="H748" t="n">
+        <v>83</v>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J748"/>
+  <dimension ref="A1:J749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33352,6 +33352,50 @@
       </c>
       <c r="J748" t="inlineStr"/>
     </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>21:14:36</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0569 cargada con 15 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>TPM-0569</t>
+        </is>
+      </c>
+      <c r="H749" t="n">
+        <v>15</v>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J749"/>
+  <dimension ref="A1:J750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33396,6 +33396,50 @@
       </c>
       <c r="J749" t="inlineStr"/>
     </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>21:14:39</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0570 cargada con 8 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>TPM-0570</t>
+        </is>
+      </c>
+      <c r="H750" t="n">
+        <v>8</v>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J750"/>
+  <dimension ref="A1:J751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33440,6 +33440,50 @@
       </c>
       <c r="J750" t="inlineStr"/>
     </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>21:14:41</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0571 cargada con 36 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>TPM-0571</t>
+        </is>
+      </c>
+      <c r="H751" t="n">
+        <v>36</v>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J751"/>
+  <dimension ref="A1:J752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33484,6 +33484,50 @@
       </c>
       <c r="J751" t="inlineStr"/>
     </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>21:14:43</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0572 cargada con 75 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="H752" t="n">
+        <v>75</v>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J752"/>
+  <dimension ref="A1:J753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33528,6 +33528,50 @@
       </c>
       <c r="J752" t="inlineStr"/>
     </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>21:14:45</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0573 cargada con 17 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>TPM-0573</t>
+        </is>
+      </c>
+      <c r="H753" t="n">
+        <v>17</v>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J753"/>
+  <dimension ref="A1:J754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33572,6 +33572,50 @@
       </c>
       <c r="J753" t="inlineStr"/>
     </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>21:14:47</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0574 cargada con 32 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>TPM-0574</t>
+        </is>
+      </c>
+      <c r="H754" t="n">
+        <v>32</v>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J754"/>
+  <dimension ref="A1:J755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33616,6 +33616,50 @@
       </c>
       <c r="J754" t="inlineStr"/>
     </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>22:56:17</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0575 cargada con 77 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="H755" t="n">
+        <v>77</v>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J755"/>
+  <dimension ref="A1:J756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33660,6 +33660,50 @@
       </c>
       <c r="J755" t="inlineStr"/>
     </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>15:23:06</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0576 cargada con 6 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>TPM-0576</t>
+        </is>
+      </c>
+      <c r="H756" t="n">
+        <v>6</v>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>PO 2609-3836</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J756"/>
+  <dimension ref="A1:J757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33704,6 +33704,50 @@
       </c>
       <c r="J756" t="inlineStr"/>
     </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>15:24:20</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Remisión E0146 generada con 1 tarima(s) y 6 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>E0146</t>
+        </is>
+      </c>
+      <c r="H757" t="n">
+        <v>6</v>
+      </c>
+      <c r="I757" t="inlineStr"/>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J757"/>
+  <dimension ref="A1:J758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33748,6 +33748,50 @@
         </is>
       </c>
     </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>15:24:23</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0576 marcada como Remesada en E0146 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>TPM-0576</t>
+        </is>
+      </c>
+      <c r="H758" t="n">
+        <v>0</v>
+      </c>
+      <c r="I758" t="inlineStr"/>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J758"/>
+  <dimension ref="A1:J759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33792,6 +33792,50 @@
         </is>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>18:16:17</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Remisión E0147 generada con 3 tarima(s) y 278 piezas hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>E0147</t>
+        </is>
+      </c>
+      <c r="H759" t="n">
+        <v>278</v>
+      </c>
+      <c r="I759" t="inlineStr"/>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J759"/>
+  <dimension ref="A1:J760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33836,6 +33836,50 @@
         </is>
       </c>
     </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>18:16:19</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0567 marcada como Remesada en E0147 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="H760" t="n">
+        <v>0</v>
+      </c>
+      <c r="I760" t="inlineStr"/>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J760"/>
+  <dimension ref="A1:J761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33880,6 +33880,50 @@
         </is>
       </c>
     </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>18:16:22</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0568 marcada como Remesada en E0147 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="H761" t="n">
+        <v>0</v>
+      </c>
+      <c r="I761" t="inlineStr"/>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J761"/>
+  <dimension ref="A1:J762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33924,6 +33924,50 @@
         </is>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>18:16:24</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0575 marcada como Remesada en E0147 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="H762" t="n">
+        <v>0</v>
+      </c>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J762"/>
+  <dimension ref="A1:J763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33968,6 +33968,50 @@
         </is>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>16:39:12</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0577 cargada con 268 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="H763" t="n">
+        <v>268</v>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J763"/>
+  <dimension ref="A1:J764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34012,6 +34012,50 @@
       </c>
       <c r="J763" t="inlineStr"/>
     </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>16:43:16</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Remisión E0148 generada con 3 tarima(s) y 397 piezas hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>E0148</t>
+        </is>
+      </c>
+      <c r="H764" t="n">
+        <v>397</v>
+      </c>
+      <c r="I764" t="inlineStr"/>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J764"/>
+  <dimension ref="A1:J765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34056,6 +34056,50 @@
         </is>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>18:49:04</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0580 cargada con 2 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>TPM-0580</t>
+        </is>
+      </c>
+      <c r="H765" t="n">
+        <v>2</v>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>PO 2609-3837</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J765"/>
+  <dimension ref="A1:J766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34100,6 +34100,50 @@
       </c>
       <c r="J765" t="inlineStr"/>
     </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>18:50:41</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Remisión E0149 generada con 1 tarima(s) y 2 piezas hacia EQM</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>E0149</t>
+        </is>
+      </c>
+      <c r="H766" t="n">
+        <v>2</v>
+      </c>
+      <c r="I766" t="inlineStr"/>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J766"/>
+  <dimension ref="A1:J767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34144,6 +34144,50 @@
         </is>
       </c>
     </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>18:50:43</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0580 marcada como Remesada en E0149 hacia EQM</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>TPM-0580</t>
+        </is>
+      </c>
+      <c r="H767" t="n">
+        <v>0</v>
+      </c>
+      <c r="I767" t="inlineStr"/>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J767"/>
+  <dimension ref="A1:J768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34188,6 +34188,50 @@
         </is>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>02:39:34</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Remisión E0143 generada hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>E0143</t>
+        </is>
+      </c>
+      <c r="H768" t="n">
+        <v>0</v>
+      </c>
+      <c r="I768" t="inlineStr"/>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J768"/>
+  <dimension ref="A1:J769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34232,6 +34232,50 @@
         </is>
       </c>
     </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>17:36:09</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0581 cargada con 1 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>TPM-0581</t>
+        </is>
+      </c>
+      <c r="H769" t="n">
+        <v>1</v>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J769"/>
+  <dimension ref="A1:J770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34276,6 +34276,50 @@
       </c>
       <c r="J769" t="inlineStr"/>
     </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>17:36:59</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Remisión E0150 generada con 1 tarima(s) y 1 piezas hacia EQM</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>E0150</t>
+        </is>
+      </c>
+      <c r="H770" t="n">
+        <v>1</v>
+      </c>
+      <c r="I770" t="inlineStr"/>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J770"/>
+  <dimension ref="A1:J771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34320,6 +34320,50 @@
         </is>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>770</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>17:37:01</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0581 marcada como Remesada en E0150 hacia EQM</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>TPM-0581</t>
+        </is>
+      </c>
+      <c r="H771" t="n">
+        <v>0</v>
+      </c>
+      <c r="I771" t="inlineStr"/>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J771"/>
+  <dimension ref="A1:J772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34364,6 +34364,50 @@
         </is>
       </c>
     </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>771</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>21:46:54</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0582 cargada con 389 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="H772" t="n">
+        <v>389</v>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J772"/>
+  <dimension ref="A1:J773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34408,6 +34408,50 @@
       </c>
       <c r="J772" t="inlineStr"/>
     </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>772</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>22:36:47</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Remisión E0153 generada con 1 tarima(s) y 7 piezas hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>E0153</t>
+        </is>
+      </c>
+      <c r="H773" t="n">
+        <v>7</v>
+      </c>
+      <c r="I773" t="inlineStr"/>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J773"/>
+  <dimension ref="A1:J775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34452,6 +34452,94 @@
         </is>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>773</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>00:48:39</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Remisión E0151 generada hacia EQM</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>E0151</t>
+        </is>
+      </c>
+      <c r="H774" t="n">
+        <v>0</v>
+      </c>
+      <c r="I774" t="inlineStr"/>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>774</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>00:48:39</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Remisión E0152 generada hacia EQM</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>E0152</t>
+        </is>
+      </c>
+      <c r="H775" t="n">
+        <v>0</v>
+      </c>
+      <c r="I775" t="inlineStr"/>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J775"/>
+  <dimension ref="A1:J776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34540,6 +34540,50 @@
         </is>
       </c>
     </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>775</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>15:31:10</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0583 cargada con 14 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="H776" t="n">
+        <v>14</v>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J776"/>
+  <dimension ref="A1:J777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34584,6 +34584,50 @@
       </c>
       <c r="J776" t="inlineStr"/>
     </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>776</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>22:46:37</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0585 cargada con 14 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>TPM-0585</t>
+        </is>
+      </c>
+      <c r="H777" t="n">
+        <v>14</v>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J777"/>
+  <dimension ref="A1:J778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34628,6 +34628,50 @@
       </c>
       <c r="J777" t="inlineStr"/>
     </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>777</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>22:50:08</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Remisión E0154 generada con 2 tarima(s) y 402 piezas hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>E0154</t>
+        </is>
+      </c>
+      <c r="H778" t="n">
+        <v>402</v>
+      </c>
+      <c r="I778" t="inlineStr"/>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J778"/>
+  <dimension ref="A1:J779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34672,6 +34672,50 @@
         </is>
       </c>
     </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>778</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>22:43:39</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0586 cargada con 461 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="H779" t="n">
+        <v>461</v>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J779"/>
+  <dimension ref="A1:J780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34716,6 +34716,50 @@
       </c>
       <c r="J779" t="inlineStr"/>
     </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>779</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>22:45:47</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Remisión E0155 generada con 4 tarima(s) y 505 piezas hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>E0155</t>
+        </is>
+      </c>
+      <c r="H780" t="n">
+        <v>505</v>
+      </c>
+      <c r="I780" t="inlineStr"/>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J780"/>
+  <dimension ref="A1:J781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34760,6 +34760,50 @@
         </is>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>780</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>22:45:50</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0589 marcada como Remesada en E0155 hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>TPM-0589</t>
+        </is>
+      </c>
+      <c r="H781" t="n">
+        <v>0</v>
+      </c>
+      <c r="I781" t="inlineStr"/>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J781"/>
+  <dimension ref="A1:J782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34804,6 +34804,50 @@
         </is>
       </c>
     </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>781</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>01:08:58</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0590 cargada con 9 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>TPM-0590</t>
+        </is>
+      </c>
+      <c r="H782" t="n">
+        <v>9</v>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>PO-RUGENCIA</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J782"/>
+  <dimension ref="A1:J783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34848,6 +34848,50 @@
       </c>
       <c r="J782" t="inlineStr"/>
     </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>782</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>01:09:46</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Remisión E0156 generada con 3 tarima(s) y 27 piezas hacia PLANTA RIO XIX</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>E0156</t>
+        </is>
+      </c>
+      <c r="H783" t="n">
+        <v>27</v>
+      </c>
+      <c r="I783" t="inlineStr"/>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>PLANTA RIO XIX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J783"/>
+  <dimension ref="A1:J784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34892,6 +34892,50 @@
         </is>
       </c>
     </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>783</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>18:48:46</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0593 cargada con 15 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>TPM-0593</t>
+        </is>
+      </c>
+      <c r="H784" t="n">
+        <v>15</v>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J784"/>
+  <dimension ref="A1:J785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34936,6 +34936,50 @@
       </c>
       <c r="J784" t="inlineStr"/>
     </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>784</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>18:59:29</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0616 cargada con 72 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="H785" t="n">
+        <v>72</v>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>PO 2608-3358; PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J785"/>
+  <dimension ref="A1:J786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34980,6 +34980,50 @@
       </c>
       <c r="J785" t="inlineStr"/>
     </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>785</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>22:09:39</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0621 cargada con 1 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>TPM-0621</t>
+        </is>
+      </c>
+      <c r="H786" t="n">
+        <v>1</v>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>PO 2610-4061</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J786"/>
+  <dimension ref="A1:J787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35024,6 +35024,50 @@
       </c>
       <c r="J786" t="inlineStr"/>
     </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>786</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>22:10:46</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Remisión E0157 generada con 1 tarima(s) y 1 piezas hacia EQM</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>E0157</t>
+        </is>
+      </c>
+      <c r="H787" t="n">
+        <v>1</v>
+      </c>
+      <c r="I787" t="inlineStr"/>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>EQM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J787"/>
+  <dimension ref="A1:J788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35068,6 +35068,50 @@
         </is>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>787</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>16:44:14</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0622 cargada con 15 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>TPM-0622</t>
+        </is>
+      </c>
+      <c r="H788" t="n">
+        <v>15</v>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>PO 2602-0711; PO 2608-3358; P0-2603-2838</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J788"/>
+  <dimension ref="A1:J789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35112,6 +35112,50 @@
       </c>
       <c r="J788" t="inlineStr"/>
     </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>788</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>16:55:39</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Remisión E0159 generada con 6 tarima(s) y 569 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>E0159</t>
+        </is>
+      </c>
+      <c r="H789" t="n">
+        <v>569</v>
+      </c>
+      <c r="I789" t="inlineStr"/>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J789"/>
+  <dimension ref="A1:J790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35156,6 +35156,50 @@
         </is>
       </c>
     </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>789</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>17:28:10</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>TARIMA_NUEVA</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Nueva tarima TPM-0635 cargada con 4 piezas (Cuadrada)</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>TPM-0635</t>
+        </is>
+      </c>
+      <c r="H790" t="n">
+        <v>4</v>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J790"/>
+  <dimension ref="A1:J791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35200,6 +35200,50 @@
       </c>
       <c r="J790" t="inlineStr"/>
     </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>790</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>17:29:29</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Remisión E0160 generada con 2 tarima(s) y 20 piezas hacia Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>E0160</t>
+        </is>
+      </c>
+      <c r="H791" t="n">
+        <v>20</v>
+      </c>
+      <c r="I791" t="inlineStr"/>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J791"/>
+  <dimension ref="A1:J792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35244,6 +35244,50 @@
         </is>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>791</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>17:29:31</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0635 marcada como Remesada en E0160 hacia Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>TPM-0635</t>
+        </is>
+      </c>
+      <c r="H792" t="n">
+        <v>0</v>
+      </c>
+      <c r="I792" t="inlineStr"/>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J792"/>
+  <dimension ref="A1:J793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35288,6 +35288,50 @@
         </is>
       </c>
     </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>792</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>17:29:33</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0633 marcada como Remesada en E0160 hacia Galvatec Industrias</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="H793" t="n">
+        <v>0</v>
+      </c>
+      <c r="I793" t="inlineStr"/>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>Galvatec Industrias</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J793"/>
+  <dimension ref="A1:J794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35332,6 +35332,50 @@
         </is>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>793</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>17:31:05</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Remisión E0160 generada con 2 tarima(s) y 20 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>E0160</t>
+        </is>
+      </c>
+      <c r="H794" t="n">
+        <v>20</v>
+      </c>
+      <c r="I794" t="inlineStr"/>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J794"/>
+  <dimension ref="A1:J795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35376,6 +35376,50 @@
         </is>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>794</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>17:31:07</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0635 marcada como Remesada en E0160 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>TPM-0635</t>
+        </is>
+      </c>
+      <c r="H795" t="n">
+        <v>0</v>
+      </c>
+      <c r="I795" t="inlineStr"/>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J795"/>
+  <dimension ref="A1:J796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35420,6 +35420,50 @@
         </is>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>795</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>17:31:09</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0633 marcada como Remesada en E0160 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="H796" t="n">
+        <v>0</v>
+      </c>
+      <c r="I796" t="inlineStr"/>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J796"/>
+  <dimension ref="A1:J797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35464,6 +35464,50 @@
         </is>
       </c>
     </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>796</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>16:09:49</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Remisión E0161 generada con 6 tarima(s) y 113 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>E0161</t>
+        </is>
+      </c>
+      <c r="H797" t="n">
+        <v>113</v>
+      </c>
+      <c r="I797" t="inlineStr"/>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J797"/>
+  <dimension ref="A1:J798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35508,6 +35508,50 @@
         </is>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>797</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>16:40:11</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Remisión E0162 generada con 3 tarima(s) y 142 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>E0162</t>
+        </is>
+      </c>
+      <c r="H798" t="n">
+        <v>142</v>
+      </c>
+      <c r="I798" t="inlineStr"/>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J798"/>
+  <dimension ref="A1:J799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35552,6 +35552,50 @@
         </is>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>798</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>18:21:29</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Remisión E0163 generada con 6 tarima(s) y 116 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>E0163</t>
+        </is>
+      </c>
+      <c r="H799" t="n">
+        <v>116</v>
+      </c>
+      <c r="I799" t="inlineStr"/>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J799"/>
+  <dimension ref="A1:J800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35596,6 +35596,50 @@
         </is>
       </c>
     </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>799</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>18:21:32</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0599 marcada como Remesada en E0163 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>TPM-0599</t>
+        </is>
+      </c>
+      <c r="H800" t="n">
+        <v>0</v>
+      </c>
+      <c r="I800" t="inlineStr"/>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J800"/>
+  <dimension ref="A1:J801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35640,6 +35640,50 @@
         </is>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>800</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>18:21:34</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0603 marcada como Remesada en E0163 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>TPM-0603</t>
+        </is>
+      </c>
+      <c r="H801" t="n">
+        <v>0</v>
+      </c>
+      <c r="I801" t="inlineStr"/>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J801"/>
+  <dimension ref="A1:J802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35684,6 +35684,50 @@
         </is>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>801</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>18:21:37</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0604 marcada como Remesada en E0163 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>TPM-0604</t>
+        </is>
+      </c>
+      <c r="H802" t="n">
+        <v>0</v>
+      </c>
+      <c r="I802" t="inlineStr"/>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J802"/>
+  <dimension ref="A1:J803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35728,6 +35728,50 @@
         </is>
       </c>
     </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>802</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>18:21:39</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0605 marcada como Remesada en E0163 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>TPM-0605</t>
+        </is>
+      </c>
+      <c r="H803" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" t="inlineStr"/>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J803"/>
+  <dimension ref="A1:J804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35772,6 +35772,50 @@
         </is>
       </c>
     </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>803</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>18:21:41</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0611 marcada como Remesada en E0163 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>TPM-0611</t>
+        </is>
+      </c>
+      <c r="H804" t="n">
+        <v>0</v>
+      </c>
+      <c r="I804" t="inlineStr"/>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J804"/>
+  <dimension ref="A1:J805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35816,6 +35816,50 @@
         </is>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>804</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>18:21:44</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>TARIMA_REMESADA</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Tarima TPM-0613 marcada como Remesada en E0163 hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>TPM-0613</t>
+        </is>
+      </c>
+      <c r="H805" t="n">
+        <v>0</v>
+      </c>
+      <c r="I805" t="inlineStr"/>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Actividad_Log.xlsx
+++ b/BD_Actividad_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J805"/>
+  <dimension ref="A1:J806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35860,6 +35860,50 @@
         </is>
       </c>
     </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>805</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>18:32:21</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>REMISION_NUEVA</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Remisión E0164 generada con 3 tarima(s) y 89 piezas hacia kirbymex</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>E0164</t>
+        </is>
+      </c>
+      <c r="H806" t="n">
+        <v>89</v>
+      </c>
+      <c r="I806" t="inlineStr"/>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>kirbymex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
